--- a/data/trans_orig/P2A_lim_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20321</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29756</t>
+          <t>33189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250993</t>
+          <t>250472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265285</t>
+          <t>265165</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>244526</t>
+          <t>243650</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256370</t>
+          <t>255976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>501169</t>
+          <t>497736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518820</t>
+          <t>518313</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36037</t>
+          <t>36153</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64986</t>
+          <t>65425</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41779</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86139</t>
+          <t>84501</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125922</t>
+          <t>125123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>428089</t>
+          <t>427650</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>457038</t>
+          <t>456922</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462170</t>
+          <t>461603</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>871102</t>
+          <t>871901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>910885</t>
+          <t>912523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>16763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>11537</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29622</t>
+          <t>29438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302862</t>
+          <t>302083</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314914</t>
+          <t>314645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>316748</t>
+          <t>318106</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330158</t>
+          <t>330398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624636</t>
+          <t>624820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642071</t>
+          <t>642721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30058</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>13803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31587</t>
+          <t>32153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30431</t>
+          <t>31303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55276</t>
+          <t>55303</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325612</t>
+          <t>325285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343443</t>
+          <t>343274</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339869</t>
+          <t>339303</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357369</t>
+          <t>357653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>671850</t>
+          <t>671823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>696695</t>
+          <t>695823</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29399</t>
+          <t>30024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17290</t>
+          <t>17905</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36837</t>
+          <t>37460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36069</t>
+          <t>35459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60352</t>
+          <t>61154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173909</t>
+          <t>173284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190483</t>
+          <t>190646</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170831</t>
+          <t>170208</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190378</t>
+          <t>189763</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>350624</t>
+          <t>349822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374907</t>
+          <t>375517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>20821</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259876</t>
+          <t>260011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267806</t>
+          <t>267810</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262656</t>
+          <t>261980</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274226</t>
+          <t>274289</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>526799</t>
+          <t>526116</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>540148</t>
+          <t>540620</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32098</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55913</t>
+          <t>57305</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38423</t>
+          <t>37050</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65636</t>
+          <t>64574</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,47 +2841,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>93199</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>75439</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>112189</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>6,02%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>93199</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>76644</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>114253</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>559114</t>
+          <t>557722</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>582929</t>
+          <t>583998</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>572583</t>
+          <t>573645</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>601169</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,47 +2954,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>94,19%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1129</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1160047</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1141057</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1177807</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>92,56%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>91,05%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>93,98%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1129</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1160047</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1138993</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1176602</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>90,88%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47536</t>
+          <t>47058</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77324</t>
+          <t>77945</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73540</t>
+          <t>75914</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>109870</t>
+          <t>111797</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130645</t>
+          <t>129478</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176551</t>
+          <t>177924</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>663909</t>
+          <t>663288</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>693697</t>
+          <t>694175</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>670593</t>
+          <t>668666</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>706923</t>
+          <t>704549</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1345145</t>
+          <t>1343772</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1391051</t>
+          <t>1392218</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>189845</t>
+          <t>189776</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>247810</t>
+          <t>248188</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>241531</t>
+          <t>239778</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>307359</t>
+          <t>302984</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>448730</t>
+          <t>449897</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>532442</t>
+          <t>534914</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3019456</t>
+          <t>3019078</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3077421</t>
+          <t>3077490</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3067562</t>
+          <t>3071937</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3133390</t>
+          <t>3135143</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6109745</t>
+          <t>6107273</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6193457</t>
+          <t>6192290</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27126</t>
+          <t>27352</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52110</t>
+          <t>52041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37140</t>
+          <t>36790</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66578</t>
+          <t>65344</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71012</t>
+          <t>69488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108557</t>
+          <t>108196</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242628</t>
+          <t>242697</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267612</t>
+          <t>267386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220667</t>
+          <t>221901</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250105</t>
+          <t>250455</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>473426</t>
+          <t>473787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>510971</t>
+          <t>512495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,06%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37661</t>
+          <t>37483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68467</t>
+          <t>67061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42170</t>
+          <t>40854</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70448</t>
+          <t>69254</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85791</t>
+          <t>86725</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125782</t>
+          <t>126137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>437060</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>467866</t>
+          <t>468044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>453317</t>
+          <t>454511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>481595</t>
+          <t>482911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>903510</t>
+          <t>903155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>943501</t>
+          <t>942567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>21267</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46093</t>
+          <t>44476</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22585</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44997</t>
+          <t>45079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48735</t>
+          <t>49790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81541</t>
+          <t>82409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277953</t>
+          <t>279570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302829</t>
+          <t>302779</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>296023</t>
+          <t>295941</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>318435</t>
+          <t>318596</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>583525</t>
+          <t>582657</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>616331</t>
+          <t>615276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37854</t>
+          <t>37727</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39634</t>
+          <t>38641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67294</t>
+          <t>65913</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61558</t>
+          <t>62516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97157</t>
+          <t>95703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336128</t>
+          <t>336255</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356766</t>
+          <t>356994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>321657</t>
+          <t>323038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349317</t>
+          <t>350310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>665776</t>
+          <t>667230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>701375</t>
+          <t>700417</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33026</t>
+          <t>32900</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58100</t>
+          <t>58849</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38354</t>
+          <t>37873</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63958</t>
+          <t>61872</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77548</t>
+          <t>77533</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112497</t>
+          <t>113141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154518</t>
+          <t>153769</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179592</t>
+          <t>179718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155633</t>
+          <t>157719</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>181237</t>
+          <t>181718</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>319712</t>
+          <t>319068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>354661</t>
+          <t>354676</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13099</t>
+          <t>12992</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31930</t>
+          <t>30690</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26142</t>
+          <t>25808</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48805</t>
+          <t>49423</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44563</t>
+          <t>44945</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74907</t>
+          <t>74760</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>242051</t>
+          <t>243291</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260882</t>
+          <t>260989</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231226</t>
+          <t>230608</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>253889</t>
+          <t>254223</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479105</t>
+          <t>479252</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509449</t>
+          <t>509067</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39854</t>
+          <t>39685</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68852</t>
+          <t>68713</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50999</t>
+          <t>48965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80766</t>
+          <t>82902</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97837</t>
+          <t>95616</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141932</t>
+          <t>141267</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592950</t>
+          <t>593089</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>621948</t>
+          <t>622117</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>611192</t>
+          <t>609056</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>640959</t>
+          <t>642993</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1211829</t>
+          <t>1212494</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1255924</t>
+          <t>1258145</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47991</t>
+          <t>46695</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>79396</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56313</t>
+          <t>55720</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90560</t>
+          <t>90626</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>110667</t>
+          <t>111082</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>156839</t>
+          <t>157446</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>696918</t>
+          <t>697522</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>728927</t>
+          <t>730223</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>733293</t>
+          <t>733227</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>767540</t>
+          <t>768133</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1443932</t>
+          <t>1443325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1490104</t>
+          <t>1489689</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>291937</t>
+          <t>290109</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>365686</t>
+          <t>363057</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>372104</t>
+          <t>371795</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>450408</t>
+          <t>454340</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>683949</t>
+          <t>684420</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>785386</t>
+          <t>792609</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3057926</t>
+          <t>3060555</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3131675</t>
+          <t>3133503</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3106006</t>
+          <t>3102074</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3184310</t>
+          <t>3184619</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6194641</t>
+          <t>6187418</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6296078</t>
+          <t>6295607</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>35403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25955</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48570</t>
+          <t>49331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45233</t>
+          <t>46529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77385</t>
+          <t>75862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258345</t>
+          <t>258358</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278464</t>
+          <t>278254</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240133</t>
+          <t>239372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262748</t>
+          <t>263655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>505079</t>
+          <t>506602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>537231</t>
+          <t>535935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>12173</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29810</t>
+          <t>29981</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>18900</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40247</t>
+          <t>39980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36097</t>
+          <t>34970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63649</t>
+          <t>63342</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461603</t>
+          <t>461432</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>478976</t>
+          <t>479240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>477746</t>
+          <t>478013</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499235</t>
+          <t>499093</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945756</t>
+          <t>946063</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>973308</t>
+          <t>974435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13190</t>
+          <t>13540</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24305</t>
+          <t>23922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32911</t>
+          <t>32719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305375</t>
+          <t>305025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316073</t>
+          <t>315427</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312004</t>
+          <t>312387</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327285</t>
+          <t>327022</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621963</t>
+          <t>622155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641164</t>
+          <t>641253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29120</t>
+          <t>27940</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54431</t>
+          <t>52651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38157</t>
+          <t>38256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67571</t>
+          <t>66369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73776</t>
+          <t>73304</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111153</t>
+          <t>114124</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315533</t>
+          <t>317313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>340844</t>
+          <t>342024</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>319712</t>
+          <t>320914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349126</t>
+          <t>349027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>646094</t>
+          <t>643123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>683471</t>
+          <t>683943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27309</t>
+          <t>26610</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>10925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27619</t>
+          <t>27979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26080</t>
+          <t>26023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49211</t>
+          <t>49368</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183912</t>
+          <t>184611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200348</t>
+          <t>200314</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>190968</t>
+          <t>190608</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206807</t>
+          <t>207662</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>380597</t>
+          <t>380440</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>403728</t>
+          <t>403785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>18079</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37515</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>22942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43935</t>
+          <t>44706</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45995</t>
+          <t>45882</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76374</t>
+          <t>77174</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225608</t>
+          <t>224899</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245172</t>
+          <t>245044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229180</t>
+          <t>228409</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251145</t>
+          <t>250173</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>459864</t>
+          <t>459064</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>490243</t>
+          <t>490356</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>24063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48699</t>
+          <t>48165</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37847</t>
+          <t>36884</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67969</t>
+          <t>66647</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69220</t>
+          <t>66826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>105772</t>
+          <t>106951</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602295</t>
+          <t>602829</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>627328</t>
+          <t>626931</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>621370</t>
+          <t>622692</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>651492</t>
+          <t>652455</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1234561</t>
+          <t>1233382</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1271113</t>
+          <t>1273507</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51548</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86075</t>
+          <t>84984</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59003</t>
+          <t>57638</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94039</t>
+          <t>94220</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>121128</t>
+          <t>119983</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170853</t>
+          <t>169820</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>692508</t>
+          <t>693599</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>727035</t>
+          <t>726282</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>732128</t>
+          <t>731947</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>767164</t>
+          <t>768529</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1433897</t>
+          <t>1434930</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1483622</t>
+          <t>1484767</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>207562</t>
+          <t>206871</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>272160</t>
+          <t>269362</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>274838</t>
+          <t>275698</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>343545</t>
+          <t>343640</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>501359</t>
+          <t>500086</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>591663</t>
+          <t>596343</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3105464</t>
+          <t>3108262</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3170062</t>
+          <t>3170753</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3193951</t>
+          <t>3193856</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3262658</t>
+          <t>3261798</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6323456</t>
+          <t>6318776</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6413760</t>
+          <t>6415033</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24778</t>
+          <t>24511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48371</t>
+          <t>48473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,82 +10717,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>15,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>40947</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31254</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>52249</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>14,14%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>18,04%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>75932</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>61276</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>93334</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>10,19%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>15,53%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>40947</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>32041</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>51513</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>75932</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>63018</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>94321</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263072</t>
+          <t>262970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286665</t>
+          <t>286932</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,82 +10830,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>84,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>248688</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>237386</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>258381</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>85,86%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>81,96%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>89,21%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>525145</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>507743</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>539801</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>87,37%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>84,47%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>248688</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>238122</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>257594</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>85,86%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>82,21%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>525145</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>506756</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>538059</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>87,37%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>84,31%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80874</t>
+          <t>79652</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122346</t>
+          <t>122013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80312</t>
+          <t>82107</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111581</t>
+          <t>111969</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>169458</t>
+          <t>167103</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>223668</t>
+          <t>219314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>392083</t>
+          <t>392416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433555</t>
+          <t>434777</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>401331</t>
+          <t>400943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432600</t>
+          <t>430805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>803673</t>
+          <t>808027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>857883</t>
+          <t>860238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,73%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39083</t>
+          <t>39577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64043</t>
+          <t>64716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37148</t>
+          <t>36322</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57887</t>
+          <t>56167</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82597</t>
+          <t>82063</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114787</t>
+          <t>114527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>251093</t>
+          <t>250420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276053</t>
+          <t>275559</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>291241</t>
+          <t>292961</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>311980</t>
+          <t>312806</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>549477</t>
+          <t>549737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>581667</t>
+          <t>582201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39739</t>
+          <t>38734</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38890</t>
+          <t>38446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35803</t>
+          <t>36908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69825</t>
+          <t>70054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>270528</t>
+          <t>271533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>294776</t>
+          <t>293857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>436828</t>
+          <t>437272</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459884</t>
+          <t>459872</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>716160</t>
+          <t>715931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750182</t>
+          <t>749077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>21233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11512</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>30136</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24257</t>
+          <t>23871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46450</t>
+          <t>46054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151336</t>
+          <t>151437</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>162877</t>
+          <t>163299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>219230</t>
+          <t>219566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>238190</t>
+          <t>238484</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375922</t>
+          <t>376318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>398115</t>
+          <t>398501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54994</t>
+          <t>54740</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>78630</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51913</t>
+          <t>51331</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72629</t>
+          <t>72984</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113831</t>
+          <t>111934</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146380</t>
+          <t>143888</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>189633</t>
+          <t>191006</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214642</t>
+          <t>214896</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>184427</t>
+          <t>184072</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205143</t>
+          <t>205725</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>380312</t>
+          <t>382804</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>412861</t>
+          <t>414758</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,75%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79375</t>
+          <t>78696</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>117509</t>
+          <t>118211</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149724</t>
+          <t>148875</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>587633</t>
+          <t>585391</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>241247</t>
+          <t>242152</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>823551</t>
+          <t>851987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>499105</t>
+          <t>498403</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>537239</t>
+          <t>537918</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>259409</t>
+          <t>261651</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>697318</t>
+          <t>698167</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>640105</t>
+          <t>611669</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1222409</t>
+          <t>1221504</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23144</t>
+          <t>24161</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78394</t>
+          <t>78635</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57466</t>
+          <t>56939</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83798</t>
+          <t>81854</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70555</t>
+          <t>74976</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>153090</t>
+          <t>152085</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>848504</t>
+          <t>848263</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>903754</t>
+          <t>902737</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>630698</t>
+          <t>632642</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>657030</t>
+          <t>657557</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1488304</t>
+          <t>1489309</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1570839</t>
+          <t>1566418</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>351263</t>
+          <t>338505</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>498687</t>
+          <t>500210</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>499800</t>
+          <t>496321</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1225374</t>
+          <t>1231422</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>928987</t>
+          <t>927262</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1976213</t>
+          <t>1857005</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2938406</t>
+          <t>2936883</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3085830</t>
+          <t>3098588</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2470313</t>
+          <t>2464265</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3195887</t>
+          <t>3199366</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5156566</t>
+          <t>5275774</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6203792</t>
+          <t>6205517</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_lim_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>20308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33189</t>
+          <t>30331</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250472</t>
+          <t>251006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265165</t>
+          <t>265713</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243650</t>
+          <t>243279</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255976</t>
+          <t>255582</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>497736</t>
+          <t>500594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518313</t>
+          <t>518500</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36153</t>
+          <t>36820</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65425</t>
+          <t>65402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42346</t>
+          <t>41474</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70022</t>
+          <t>68713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84501</t>
+          <t>84294</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125123</t>
+          <t>123159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>427650</t>
+          <t>427673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>456922</t>
+          <t>456255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>433927</t>
+          <t>435236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>461603</t>
+          <t>462475</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>871901</t>
+          <t>873865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>912523</t>
+          <t>912730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16763</t>
+          <t>15560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29438</t>
+          <t>29877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302083</t>
+          <t>303286</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314645</t>
+          <t>314837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318106</t>
+          <t>317414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330398</t>
+          <t>330199</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624820</t>
+          <t>624381</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642721</t>
+          <t>641933</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12396</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30385</t>
+          <t>30406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32153</t>
+          <t>31893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31303</t>
+          <t>30270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55303</t>
+          <t>54736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325285</t>
+          <t>325264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343274</t>
+          <t>343063</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339303</t>
+          <t>339563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357653</t>
+          <t>358109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>671823</t>
+          <t>672390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>695823</t>
+          <t>696856</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30024</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17905</t>
+          <t>18059</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37460</t>
+          <t>37593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35459</t>
+          <t>35338</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61154</t>
+          <t>61121</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173284</t>
+          <t>173982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190646</t>
+          <t>190439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170208</t>
+          <t>170075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189763</t>
+          <t>189609</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>349822</t>
+          <t>349855</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375517</t>
+          <t>375638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>15770</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20821</t>
+          <t>20577</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260011</t>
+          <t>259043</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267810</t>
+          <t>267776</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261980</t>
+          <t>262374</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274289</t>
+          <t>274268</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>526116</t>
+          <t>526360</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>540620</t>
+          <t>540098</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31029</t>
+          <t>32121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57305</t>
+          <t>57662</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>37529</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64574</t>
+          <t>64267</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75439</t>
+          <t>76212</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112189</t>
+          <t>112692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>557722</t>
+          <t>557365</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>583998</t>
+          <t>582906</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>573645</t>
+          <t>573952</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>601169</t>
+          <t>600690</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1141057</t>
+          <t>1140554</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1177807</t>
+          <t>1177034</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,92%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47058</t>
+          <t>47394</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77945</t>
+          <t>77833</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75914</t>
+          <t>74227</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111797</t>
+          <t>110673</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>129478</t>
+          <t>128436</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177924</t>
+          <t>177180</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>663288</t>
+          <t>663400</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>694175</t>
+          <t>693839</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>668666</t>
+          <t>669790</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>704549</t>
+          <t>706236</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1343772</t>
+          <t>1344516</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1392218</t>
+          <t>1393260</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>189776</t>
+          <t>189238</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>248188</t>
+          <t>250372</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>239778</t>
+          <t>244338</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>302984</t>
+          <t>305926</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>449897</t>
+          <t>448197</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>534914</t>
+          <t>532244</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3019078</t>
+          <t>3016894</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3077490</t>
+          <t>3078028</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3071937</t>
+          <t>3068995</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3135143</t>
+          <t>3130583</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6107273</t>
+          <t>6109943</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6192290</t>
+          <t>6193990</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27352</t>
+          <t>27063</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52041</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36790</t>
+          <t>36761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65344</t>
+          <t>64611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69488</t>
+          <t>68188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108196</t>
+          <t>106464</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242697</t>
+          <t>243662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267386</t>
+          <t>267675</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221901</t>
+          <t>222634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250455</t>
+          <t>250484</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>473787</t>
+          <t>475519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>512495</t>
+          <t>513795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37483</t>
+          <t>37038</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67061</t>
+          <t>66621</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40854</t>
+          <t>40775</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69254</t>
+          <t>69184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86725</t>
+          <t>86050</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126137</t>
+          <t>125860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>438466</t>
+          <t>438906</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>468044</t>
+          <t>468489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>454511</t>
+          <t>454581</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482911</t>
+          <t>482990</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>903155</t>
+          <t>903432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>942567</t>
+          <t>943242</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21267</t>
+          <t>21047</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>46665</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22424</t>
+          <t>22666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45079</t>
+          <t>45061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49790</t>
+          <t>48374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82409</t>
+          <t>79468</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279570</t>
+          <t>277381</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302779</t>
+          <t>302999</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>295941</t>
+          <t>295959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>318596</t>
+          <t>318354</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>582657</t>
+          <t>585598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>615276</t>
+          <t>616692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>17981</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37727</t>
+          <t>37888</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38641</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65913</t>
+          <t>65993</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62516</t>
+          <t>62165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95703</t>
+          <t>96486</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336255</t>
+          <t>336094</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356994</t>
+          <t>356001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>323038</t>
+          <t>322958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>350310</t>
+          <t>350540</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667230</t>
+          <t>666447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>700417</t>
+          <t>700768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32900</t>
+          <t>32422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58849</t>
+          <t>57931</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37873</t>
+          <t>38273</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61872</t>
+          <t>63671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77533</t>
+          <t>76119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113141</t>
+          <t>112652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153769</t>
+          <t>154687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179718</t>
+          <t>180196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157719</t>
+          <t>155920</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>181718</t>
+          <t>181318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>319068</t>
+          <t>319557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>354676</t>
+          <t>356090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>14148</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>31112</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25808</t>
+          <t>26315</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49423</t>
+          <t>50030</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44945</t>
+          <t>44200</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74760</t>
+          <t>73287</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243291</t>
+          <t>242869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260989</t>
+          <t>259833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230608</t>
+          <t>230001</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254223</t>
+          <t>253716</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479252</t>
+          <t>480725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509067</t>
+          <t>509812</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39685</t>
+          <t>41272</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68713</t>
+          <t>70920</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48965</t>
+          <t>48182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82902</t>
+          <t>80321</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95616</t>
+          <t>98438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>141267</t>
+          <t>143224</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>593089</t>
+          <t>590882</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>622117</t>
+          <t>620530</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>609056</t>
+          <t>611637</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>642993</t>
+          <t>643776</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1212494</t>
+          <t>1210537</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1258145</t>
+          <t>1255323</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46695</t>
+          <t>46627</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79396</t>
+          <t>79942</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55720</t>
+          <t>55726</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90626</t>
+          <t>90084</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>111082</t>
+          <t>111912</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>157446</t>
+          <t>157862</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>697522</t>
+          <t>696976</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>730223</t>
+          <t>730291</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>733227</t>
+          <t>733769</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>768133</t>
+          <t>768127</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1443325</t>
+          <t>1442909</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1489689</t>
+          <t>1488859</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>290109</t>
+          <t>291578</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>363057</t>
+          <t>364317</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>371795</t>
+          <t>371725</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>454340</t>
+          <t>453782</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>684420</t>
+          <t>683989</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>792609</t>
+          <t>793306</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3060555</t>
+          <t>3059295</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3133503</t>
+          <t>3132034</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3102074</t>
+          <t>3102632</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3184619</t>
+          <t>3184689</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6187418</t>
+          <t>6186721</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6295607</t>
+          <t>6296038</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15507</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35403</t>
+          <t>34962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25048</t>
+          <t>24962</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49331</t>
+          <t>48420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46529</t>
+          <t>45790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75862</t>
+          <t>77336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258358</t>
+          <t>258799</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278254</t>
+          <t>278343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239372</t>
+          <t>240283</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263655</t>
+          <t>263741</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>506602</t>
+          <t>505128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>535935</t>
+          <t>536674</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>29992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39980</t>
+          <t>41375</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34970</t>
+          <t>35780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63342</t>
+          <t>64314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461432</t>
+          <t>461421</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>479240</t>
+          <t>478937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>478013</t>
+          <t>476618</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499093</t>
+          <t>498239</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>946063</t>
+          <t>945091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974435</t>
+          <t>973625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>24733</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32719</t>
+          <t>32433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305025</t>
+          <t>304825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315427</t>
+          <t>315927</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312387</t>
+          <t>311576</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327022</t>
+          <t>327010</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622155</t>
+          <t>622441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641253</t>
+          <t>641134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>29076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52651</t>
+          <t>53026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38256</t>
+          <t>39414</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66369</t>
+          <t>67077</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73304</t>
+          <t>73390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114124</t>
+          <t>112113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>317313</t>
+          <t>316938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342024</t>
+          <t>340888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320914</t>
+          <t>320206</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349027</t>
+          <t>347869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>643123</t>
+          <t>645134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>683943</t>
+          <t>683857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>27174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>11509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27979</t>
+          <t>28143</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>25776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49368</t>
+          <t>48166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184611</t>
+          <t>184047</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200314</t>
+          <t>199996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>190608</t>
+          <t>190444</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207662</t>
+          <t>207078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>380440</t>
+          <t>381642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>403785</t>
+          <t>404032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18079</t>
+          <t>17479</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38224</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22942</t>
+          <t>22246</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44706</t>
+          <t>45879</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45882</t>
+          <t>45594</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77174</t>
+          <t>75338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224899</t>
+          <t>225000</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245044</t>
+          <t>245644</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>228409</t>
+          <t>227236</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250173</t>
+          <t>250869</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>459064</t>
+          <t>460900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>490356</t>
+          <t>490644</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24063</t>
+          <t>24958</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48165</t>
+          <t>48348</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36884</t>
+          <t>37580</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66647</t>
+          <t>70053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66826</t>
+          <t>69167</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106951</t>
+          <t>106803</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602829</t>
+          <t>602646</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>626931</t>
+          <t>626036</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>622692</t>
+          <t>619286</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>652455</t>
+          <t>651759</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1233382</t>
+          <t>1233530</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1273507</t>
+          <t>1271166</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52301</t>
+          <t>51631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84984</t>
+          <t>85066</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57638</t>
+          <t>58627</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94220</t>
+          <t>93891</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>119983</t>
+          <t>119210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>169820</t>
+          <t>167231</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>693599</t>
+          <t>693517</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>726282</t>
+          <t>726952</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>731947</t>
+          <t>732276</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>768529</t>
+          <t>767540</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1434930</t>
+          <t>1437519</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1484767</t>
+          <t>1485540</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>206871</t>
+          <t>204528</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>269362</t>
+          <t>268352</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>275777</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>343640</t>
+          <t>345368</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>500086</t>
+          <t>501779</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>596343</t>
+          <t>593632</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3108262</t>
+          <t>3109272</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3170753</t>
+          <t>3173096</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3193856</t>
+          <t>3192128</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3261798</t>
+          <t>3261719</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6318776</t>
+          <t>6321487</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6415033</t>
+          <t>6413340</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34985</t>
+          <t>34128</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24511</t>
+          <t>23276</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48473</t>
+          <t>45970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>41656</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>32601</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52249</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>75932</t>
+          <t>75785</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61276</t>
+          <t>63022</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93334</t>
+          <t>91842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>276458</t>
+          <t>284717</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262970</t>
+          <t>272875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286932</t>
+          <t>295569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>248688</t>
+          <t>274405</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>237386</t>
+          <t>263701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258381</t>
+          <t>283460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>525145</t>
+          <t>559121</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>507743</t>
+          <t>543064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>539801</t>
+          <t>571884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,07%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>98843</t>
+          <t>100833</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79652</t>
+          <t>80786</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122013</t>
+          <t>124040</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95835</t>
+          <t>101575</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82107</t>
+          <t>86372</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111969</t>
+          <t>118292</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>194678</t>
+          <t>202408</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167103</t>
+          <t>177919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>219314</t>
+          <t>231090</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>415586</t>
+          <t>426506</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>392416</t>
+          <t>403299</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434777</t>
+          <t>446553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>417077</t>
+          <t>442850</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>400943</t>
+          <t>426133</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>430805</t>
+          <t>458053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>832663</t>
+          <t>869356</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>808027</t>
+          <t>840674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>860238</t>
+          <t>893845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,4%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514429</t>
+          <t>527339</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514429</t>
+          <t>527339</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514429</t>
+          <t>527339</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512912</t>
+          <t>544425</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512912</t>
+          <t>544425</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512912</t>
+          <t>544425</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1027341</t>
+          <t>1071764</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1027341</t>
+          <t>1071764</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1027341</t>
+          <t>1071764</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51309</t>
+          <t>50796</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39577</t>
+          <t>40334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64716</t>
+          <t>64344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45768</t>
+          <t>46324</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36322</t>
+          <t>37136</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56167</t>
+          <t>56939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>97077</t>
+          <t>97120</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82063</t>
+          <t>82337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114527</t>
+          <t>113769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>263827</t>
+          <t>264322</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>250420</t>
+          <t>250774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>275559</t>
+          <t>274784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>303360</t>
+          <t>310057</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292961</t>
+          <t>299442</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312806</t>
+          <t>319245</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>567187</t>
+          <t>574379</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>549737</t>
+          <t>557730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>582201</t>
+          <t>589162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,74%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315136</t>
+          <t>315118</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315136</t>
+          <t>315118</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315136</t>
+          <t>315118</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664264</t>
+          <t>671499</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664264</t>
+          <t>671499</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664264</t>
+          <t>671499</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>19171</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38734</t>
+          <t>47669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>29140</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>21666</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38446</t>
+          <t>42160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>52214</t>
+          <t>59747</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36908</t>
+          <t>46296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70054</t>
+          <t>79485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>285047</t>
+          <t>340236</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271533</t>
+          <t>323174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>293857</t>
+          <t>351672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>448724</t>
+          <t>392821</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>437272</t>
+          <t>379801</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459872</t>
+          <t>400295</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>733771</t>
+          <t>733057</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>715931</t>
+          <t>713319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749077</t>
+          <t>746508</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310267</t>
+          <t>370843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310267</t>
+          <t>370843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310267</t>
+          <t>370843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>785985</t>
+          <t>792804</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>785985</t>
+          <t>792804</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>785985</t>
+          <t>792804</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9371</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21233</t>
+          <t>21827</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>18458</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30136</t>
+          <t>30801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>36343</t>
+          <t>39472</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23871</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46054</t>
+          <t>48902</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>158367</t>
+          <t>183563</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151437</t>
+          <t>177393</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163299</t>
+          <t>188900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>227662</t>
+          <t>195106</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>219566</t>
+          <t>188120</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>238484</t>
+          <t>200463</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>386029</t>
+          <t>378669</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>376318</t>
+          <t>369239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>398501</t>
+          <t>386645</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>199220</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>199220</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172670</t>
+          <t>199220</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>249702</t>
+          <t>218921</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>249702</t>
+          <t>218921</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>249702</t>
+          <t>218921</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>422372</t>
+          <t>418141</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>422372</t>
+          <t>418141</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>422372</t>
+          <t>418141</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>66533</t>
+          <t>66441</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54740</t>
+          <t>54910</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78630</t>
+          <t>78164</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>61876</t>
+          <t>62441</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51331</t>
+          <t>52569</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72984</t>
+          <t>73379</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>128409</t>
+          <t>128882</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111934</t>
+          <t>114622</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>143888</t>
+          <t>147733</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>203103</t>
+          <t>204266</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>191006</t>
+          <t>192543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214896</t>
+          <t>215797</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>195180</t>
+          <t>201309</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>184072</t>
+          <t>190371</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205725</t>
+          <t>211181</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>398283</t>
+          <t>405575</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>382804</t>
+          <t>386724</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>414758</t>
+          <t>419835</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>97267</t>
+          <t>114028</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78696</t>
+          <t>96221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>118211</t>
+          <t>137265</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>323676</t>
+          <t>151370</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148875</t>
+          <t>132956</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>585391</t>
+          <t>174812</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>420943</t>
+          <t>265398</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>242152</t>
+          <t>236356</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>851987</t>
+          <t>299104</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>519347</t>
+          <t>593689</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>498403</t>
+          <t>570452</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>537918</t>
+          <t>611496</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>523366</t>
+          <t>618342</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>261651</t>
+          <t>594900</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>698167</t>
+          <t>636756</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1042713</t>
+          <t>1212030</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>611669</t>
+          <t>1178324</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1221504</t>
+          <t>1241072</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>616614</t>
+          <t>707717</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>616614</t>
+          <t>707717</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>616614</t>
+          <t>707717</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847042</t>
+          <t>769712</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847042</t>
+          <t>769712</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847042</t>
+          <t>769712</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1463656</t>
+          <t>1477428</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1463656</t>
+          <t>1477428</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1463656</t>
+          <t>1477428</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>53746</t>
+          <t>62220</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24161</t>
+          <t>47593</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78635</t>
+          <t>78460</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>69491</t>
+          <t>82936</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56939</t>
+          <t>68455</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81854</t>
+          <t>99509</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>123237</t>
+          <t>145156</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74976</t>
+          <t>125232</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>152085</t>
+          <t>170038</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>873152</t>
+          <t>733883</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>848263</t>
+          <t>717643</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>902737</t>
+          <t>748510</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>645005</t>
+          <t>744843</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>632642</t>
+          <t>728270</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>657557</t>
+          <t>759324</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1518157</t>
+          <t>1478727</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1489309</t>
+          <t>1453845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1566418</t>
+          <t>1498651</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>92,29%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926898</t>
+          <t>796103</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926898</t>
+          <t>796103</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926898</t>
+          <t>796103</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714496</t>
+          <t>827779</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714496</t>
+          <t>827779</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714496</t>
+          <t>827779</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1641394</t>
+          <t>1623883</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1641394</t>
+          <t>1623883</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1641394</t>
+          <t>1623883</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>442206</t>
+          <t>474711</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>338505</t>
+          <t>428364</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>500210</t>
+          <t>515490</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>686628</t>
+          <t>539257</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>496321</t>
+          <t>503319</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1231422</t>
+          <t>576475</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1128833</t>
+          <t>1013967</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>927262</t>
+          <t>957866</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1857005</t>
+          <t>1073169</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2994887</t>
+          <t>3031181</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2936883</t>
+          <t>2990402</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3098588</t>
+          <t>3077528</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3009059</t>
+          <t>3179733</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2464265</t>
+          <t>3142515</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3199366</t>
+          <t>3215671</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6003946</t>
+          <t>6210915</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5275774</t>
+          <t>6151713</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6205517</t>
+          <t>6267016</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3437093</t>
+          <t>3505892</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3437093</t>
+          <t>3505892</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3437093</t>
+          <t>3505892</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3695687</t>
+          <t>3718990</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3695687</t>
+          <t>3718990</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3695687</t>
+          <t>3718990</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7132779</t>
+          <t>7224882</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7132779</t>
+          <t>7224882</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7132779</t>
+          <t>7224882</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_lim_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
